--- a/artfynd/A 29054-2026 artfynd.xlsx
+++ b/artfynd/A 29054-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929360</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929363</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929364</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929367</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945905</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945908</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929347</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929348</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929356</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929362</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929366</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945904</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929361</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945893</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929345</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929350</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929351</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929353</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929355</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929358</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929359</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945889</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945890</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945891</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945892</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945894</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,6 +3696,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945896</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945897</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3775,6 +3920,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945899</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3882,6 +4032,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945900</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3989,6 +4144,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945901</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4096,6 +4256,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945907</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4203,6 +4368,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945902</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4310,6 +4480,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945906</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4427,6 +4602,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945910</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4539,6 +4719,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929368</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4646,6 +4831,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929352</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4753,6 +4943,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929346</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4860,6 +5055,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929354</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4967,8 +5167,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929357</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29054-2026 artfynd.xlsx
+++ b/artfynd/A 29054-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134929360</v>
       </c>
       <c r="B2" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>134929363</v>
       </c>
       <c r="B3" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>134929364</v>
       </c>
       <c r="B4" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>134929367</v>
       </c>
       <c r="B5" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>134945905</v>
       </c>
       <c r="B6" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>134945908</v>
       </c>
       <c r="B7" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>134929347</v>
       </c>
       <c r="B8" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>134929348</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>134929356</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>134929362</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>134929366</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>134945904</v>
       </c>
       <c r="B13" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>134929361</v>
       </c>
       <c r="B14" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>134945893</v>
       </c>
       <c r="B15" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>134929345</v>
       </c>
       <c r="B16" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>134929350</v>
       </c>
       <c r="B17" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>134929351</v>
       </c>
       <c r="B18" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>134929353</v>
       </c>
       <c r="B19" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>134929355</v>
       </c>
       <c r="B20" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>134929358</v>
       </c>
       <c r="B21" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>134929359</v>
       </c>
       <c r="B22" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>134945889</v>
       </c>
       <c r="B23" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>134945890</v>
       </c>
       <c r="B24" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>134945891</v>
       </c>
       <c r="B25" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>134945892</v>
       </c>
       <c r="B26" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>134945894</v>
       </c>
       <c r="B27" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>134945896</v>
       </c>
       <c r="B28" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>134945897</v>
       </c>
       <c r="B29" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>134945899</v>
       </c>
       <c r="B30" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>134945900</v>
       </c>
       <c r="B31" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>134945901</v>
       </c>
       <c r="B32" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>134945907</v>
       </c>
       <c r="B33" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>134945902</v>
       </c>
       <c r="B34" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>134945906</v>
       </c>
       <c r="B35" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>134945910</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>134929368</v>
       </c>
       <c r="B37" t="n">
-        <v>57165</v>
+        <v>57170</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>134929352</v>
       </c>
       <c r="B38" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>134929346</v>
       </c>
       <c r="B39" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>134929354</v>
       </c>
       <c r="B40" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>134929357</v>
       </c>
       <c r="B41" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
